--- a/Analisis_ABC_Productos.xlsx
+++ b/Analisis_ABC_Productos.xlsx
@@ -220,7 +220,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -372,7 +371,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -640,7 +638,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10080000" cy="5760000"/>

--- a/Analisis_ABC_Productos.xlsx
+++ b/Analisis_ABC_Productos.xlsx
@@ -220,6 +220,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -230,7 +231,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Análisis ABC — Facturación y % Acumulado</a:t>
+              <a:t>Título del gráfico</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -245,12 +246,12 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Análisis ABC'!E3</f>
+              <f>'Análisis ABC'!C3</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="1F4E79"/>
+              <a:srgbClr val="4472C4"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -258,12 +259,93 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Análisis ABC'!$B$4:$B$13</f>
+              <f>'Análisis ABC'!$A$4:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Análisis ABC'!$C$4:$C$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Análisis ABC'!D3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Análisis ABC'!$A$4:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Análisis ABC'!$D$4:$D$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Análisis ABC'!E3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="A5A5A5"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Análisis ABC'!$A$4:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Análisis ABC'!$E$4:$E$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Análisis ABC'!F3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Análisis ABC'!$A$4:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Análisis ABC'!$F$4:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -274,17 +356,17 @@
       <lineChart>
         <grouping val="standard"/>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
               <f>'Análisis ABC'!G3</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25000">
               <a:solidFill>
-                <a:srgbClr val="FF6600"/>
+                <a:srgbClr val="5B9BD5"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -312,21 +394,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Productos</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -339,21 +406,6 @@
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Facturación (€)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -361,7 +413,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -370,157 +422,6 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Análisis ABC — Unidades Vendidas y % Acumulado</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Análisis ABC'!C3</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Análisis ABC'!$B$4:$B$13</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Análisis ABC'!$C$4:$C$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Análisis ABC'!G3</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
-              <a:solidFill>
-                <a:srgbClr val="FF6600"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <val>
-            <numRef>
-              <f>'Análisis ABC'!$G$4:$G$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Productos</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Unidades vendidas</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-        <crosses val="min"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -619,7 +520,7 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10080000" cy="5760000"/>
+    <ext cx="10800000" cy="6480000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -629,28 +530,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="10080000" cy="5760000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/Analisis_ABC_Productos.xlsx
+++ b/Analisis_ABC_Productos.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Análisis ABC" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen ABC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,10 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0 €"/>
-  </numFmts>
-  <fonts count="7">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,13 +28,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -55,9 +45,6 @@
       <b val="1"/>
       <color rgb="009C0006"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -68,8 +55,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -109,12 +96,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -123,25 +107,18 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -246,7 +223,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Análisis ABC'!C3</f>
+              <f>'Hoja1'!C1</f>
             </strRef>
           </tx>
           <spPr>
@@ -259,12 +236,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Análisis ABC'!$A$4:$A$13</f>
+              <f>'Hoja1'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Análisis ABC'!$C$4:$C$13</f>
+              <f>'Hoja1'!$C$2:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -273,7 +250,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Análisis ABC'!D3</f>
+              <f>'Hoja1'!D1</f>
             </strRef>
           </tx>
           <spPr>
@@ -286,12 +263,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Análisis ABC'!$A$4:$A$13</f>
+              <f>'Hoja1'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Análisis ABC'!$D$4:$D$13</f>
+              <f>'Hoja1'!$D$2:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -300,7 +277,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Análisis ABC'!E3</f>
+              <f>'Hoja1'!E1</f>
             </strRef>
           </tx>
           <spPr>
@@ -313,12 +290,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Análisis ABC'!$A$4:$A$13</f>
+              <f>'Hoja1'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Análisis ABC'!$E$4:$E$13</f>
+              <f>'Hoja1'!$E$2:$E$11</f>
             </numRef>
           </val>
         </ser>
@@ -327,7 +304,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Análisis ABC'!F3</f>
+              <f>'Hoja1'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -340,12 +317,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Análisis ABC'!$A$4:$A$13</f>
+              <f>'Hoja1'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Análisis ABC'!$F$4:$F$13</f>
+              <f>'Hoja1'!$F$2:$F$11</f>
             </numRef>
           </val>
         </ser>
@@ -360,11 +337,11 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Análisis ABC'!G3</f>
+              <f>'Hoja1'!G1</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="5B9BD5"/>
               </a:solidFill>
@@ -381,7 +358,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Análisis ABC'!$G$4:$G$13</f>
+              <f>'Hoja1'!$G$2:$G$11</f>
             </numRef>
           </val>
         </ser>
@@ -421,133 +398,16 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Distribución ABC por Facturación</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Resumen ABC'!E3</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dPt>
-            <idx val="0"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="006100"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="BF8F00"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="2"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="9C0006"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <cat>
-            <numRef>
-              <f>'Resumen ABC'!$A$4:$A$6</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Resumen ABC'!$E$4:$E$6</f>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10800000" cy="6480000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="5040000"/>
+    <ext cx="10080000" cy="5760000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -854,563 +714,382 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ANÁLISIS ABC DE PRODUCTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Código</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Uds. vendidas/año</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Precio unit. (€)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Facturación (€)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>% Facturación</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>% Acumulado</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>% Uds.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Clasificación ABC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Aceite de oliva</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>400000</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>0.1568627450980392</v>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Conservas vegetales</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>0.196078431372549</v>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Arroz</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>150000</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Pasta</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>14000</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>70000</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>0.1098039215686274</v>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>P05</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Legumbres</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>0.07843137254901961</v>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Harina</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>0.07843137254901961</v>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>P07</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Sal</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0.07843137254901961</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>P08</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Vinagre</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>0.0392156862745098</v>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>P09</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Especias</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>0.0196078431372549</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Infusiones</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>0.007843137254901961</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="12" t="n">
-        <v>127500</v>
-      </c>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="13" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RESUMEN POR CATEGORÍA ABC</t>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unidades vendidas al año</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precio unitario (euros)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Facturación</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>% Facturación</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>% Acumulado</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Clasificación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Arroz</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Categoría</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Nº Productos</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>% Productos</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Facturación (€)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>% Facturación</t>
+          <t>Conservas vegetales</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Aceite de oliva</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>800000</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>0.8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Pasta</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>0.15</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Legumbres</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Harina</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Sal</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Vinagre</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Especias</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>0.05</v>
+      <c r="E10" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Infusiones</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/Analisis_ABC_Productos.xlsx
+++ b/Analisis_ABC_Productos.xlsx
@@ -228,7 +228,7 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
+              <a:srgbClr val="00B050"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -255,7 +255,7 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
+              <a:srgbClr val="FF0000"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -282,7 +282,7 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="A5A5A5"/>
+              <a:srgbClr val="92D050"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -309,7 +309,7 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
+              <a:srgbClr val="4472C4"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -343,7 +343,7 @@
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
-                <a:srgbClr val="5B9BD5"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -359,6 +359,36 @@
           <val>
             <numRef>
               <f>'Hoja1'!$G$2:$G$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Hoja1'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Hoja1'!$H$2:$H$11</f>
             </numRef>
           </val>
         </ser>
@@ -714,23 +744,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Código</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -750,30 +781,33 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Facturación</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>% Facturación</t>
+          <t>ACUMULADO</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>PORCENTUAL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>% Acumulado</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Clasificación</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -789,23 +823,24 @@
       <c r="E2" s="3" t="n">
         <v>150000</v>
       </c>
-      <c r="F2" s="4" t="n">
-        <v>0.15</v>
+      <c r="F2" s="3" t="n">
+        <v>150000</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -821,23 +856,24 @@
       <c r="E3" s="3" t="n">
         <v>250000</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
+      <c r="A4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -853,23 +889,24 @@
       <c r="E4" s="3" t="n">
         <v>400000</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="3" t="n">
+        <v>800000</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
+      <c r="A5" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -885,23 +922,24 @@
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="3" t="n">
+        <v>870000</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>P05</t>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -917,23 +955,24 @@
       <c r="E6" s="3" t="n">
         <v>50000</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="3" t="n">
+        <v>920000</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
+      <c r="A7" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -949,23 +988,24 @@
       <c r="E7" s="3" t="n">
         <v>30000</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="3" t="n">
+        <v>950000</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>0.03</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>P07</t>
-        </is>
+      <c r="A8" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -981,23 +1021,24 @@
       <c r="E8" s="3" t="n">
         <v>20000</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="3" t="n">
+        <v>970000</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>0.02</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>P08</t>
-        </is>
+      <c r="A9" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -1013,23 +1054,24 @@
       <c r="E9" s="3" t="n">
         <v>15000</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="3" t="n">
+        <v>985000</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>0.015</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>0.985</v>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>P09</t>
-        </is>
+      <c r="A10" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -1045,23 +1087,24 @@
       <c r="E10" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="3" t="n">
+        <v>995000</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>0.995</v>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
+      <c r="A11" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -1077,13 +1120,16 @@
       <c r="E11" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>0.005</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
